--- a/SGC-CKN/Excel/06e8ce2e-abe8-4cdd-91fe-0e125c96f0df_Cọc_D1-17_D1-17_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/06e8ce2e-abe8-4cdd-91fe-0e125c96f0df_Cọc_D1-17_D1-17_D800_19-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>D1-17</t>
+    <t>P1-171</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/06e8ce2e-abe8-4cdd-91fe-0e125c96f0df_Cọc_D1-17_D1-17_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/06e8ce2e-abe8-4cdd-91fe-0e125c96f0df_Cọc_D1-17_D1-17_D800_19-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>06:40 19/03/2026</t>
+    <t>06:48 19/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:00
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">03:00
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">04:00
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">04:50
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>Chạm Sỏi</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">06:48
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>Kết thúc tại cao độ -49.35m</t>
@@ -1413,16 +1413,16 @@
         <v>-36.16</v>
       </c>
       <c r="G18" s="29">
-        <v>-49.35</v>
+        <v>-44.35</v>
       </c>
       <c r="H18" s="29">
         <v>1.97</v>
       </c>
       <c r="I18" s="29">
-        <v>13.19</v>
-      </c>
-      <c r="J18" s="22">
-        <v>6.71</v>
+        <v>8.19</v>
+      </c>
+      <c r="J18" s="12">
+        <v>4.16</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>53</v>
@@ -1783,16 +1783,16 @@
         <v>-36.16</v>
       </c>
       <c r="F9" s="29">
-        <v>-49.35</v>
+        <v>-44.35</v>
       </c>
       <c r="G9" s="29">
         <v>1.97</v>
       </c>
       <c r="H9" s="29">
-        <v>13.19</v>
-      </c>
-      <c r="I9" s="22">
-        <v>6.71</v>
+        <v>8.19</v>
+      </c>
+      <c r="I9" s="12">
+        <v>4.16</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1812,16 +1812,16 @@
         <v>-0.67</v>
       </c>
       <c r="F10" s="34">
-        <v>-49.35</v>
+        <v>-44.35</v>
       </c>
       <c r="G10" s="34">
         <v>9.63</v>
       </c>
       <c r="H10" s="34">
-        <v>48.68</v>
+        <v>43.68</v>
       </c>
       <c r="I10" s="34">
-        <v>5.05</v>
+        <v>4.53</v>
       </c>
     </row>
   </sheetData>
